--- a/human_validation/judge/kor/judge_D005_S001_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S001_P001__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,187 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 앉으세요. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 여기 온 건 배차팀이랑 준법 부서가 컴퓨터 시스템으로 제 노선 변경 사항을 추적해 오고 있다고 생각해서예요. 무전기로도 은근히 이런저런 말들이 오가고요, 특정 운전기사들이 저에 대해 보고하고 있다는 걸 알 수 있어요, 사람들은 계속 그냥 평범한 감독일 뿐이라고 하는데도요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 배차팀이나 다른 운전기사들과 관련해서 이런 일들을 알아차린 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 이제 두 달쯤 됐어요. 그때부터 컴퓨터 추적이랑 무전기에서 오가는 말들이 저한테 꽤 분명하게 느껴지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 주변에 아무도 없을 때, 혹은 다른 사람들은 듣지 못하는데 목소리나 소리를 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 아무도 없을 때 목소리나 소리를 들은 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지난 두 달 동안 기분은 어떠셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] '기분'이 정확히 무슨 뜻인지 잘 모르겠어요. 저는 주로 직장에서 벌어지고 있는 일에 집중해 왔거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 본인 외부의 누군가 또는 무언가가 본인의 머릿속에 생각을 집어넣거나, 몸을 조종하고 있다고 느낀 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 아니요, 누가 제 머릿속에 생각을 집어넣는다거나 제 몸을 조종한다는 느낌은 아니에요. 그보다는 배차팀이랑 준법 부서가 제가 하는 일—노선 변경이나 무전기 발언 같은 걸—추적하고 있고, 다른 운전기사들 몇 명이 저에 대해 보고하고 있다는 걸 알 수 있다는 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 최근에 오락용 약물을 사용하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] '오락용 약물'이 무슨 뜻이신지 잘 모르겠어요. 딱히 그런 걸 알아차린 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 다른 신체적인 질환이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 없는 것 같아요. 무슨 질환이 있다는 얘기를 들은 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 지난 두 달 전까지는, 평소에 다른 사람들을 믿기 어렵다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 보통은 그냥 사람들을 있는 그대로 받아들이는 편이었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현병 (D005)
 인구통계: 성별 여성 / 나이 29 / 직업상태 transportation worker / 최종학력 전문학사
@@ -575,236 +747,31 @@
 증상 지속 기간: 8 months
 추가 요건: 
 주호소 증상 코드: S019
-배경 서술: 낸시가 상사의 장기 휴직 기간 동안 임시 배차 팀장을 맡아달라는 요청을 받았을 때, 그 역할은 처음에는 승진으로 이어질 수 있는 구조화된 도전처럼 보였다. 이후 8개월 동안 노선과 준법 관련 감시가 늘어나면서 고정된 믿음이 자리 잡기 시작했고, 직장과 익숙한 커뮤니티 자리에서 그녀의 행동은 점점 상황에 어울리지 않게 되었으며, 성가대, 소프트볼, 손님 초대, 자원봉사 기획에서도 손을 떼게 되었다. 늦여름 무렵에는 노선 보고서가 지연되고, 운전기사들은 그녀의 지시를 따르기 어렵다고 불평했으며, 남편은 집에서 그녀가 의지하던 정돈된 일상이 대부분 무너졌다는 것을 알아챘다. 그녀는 직장에서 직원 지원 프로그램을 통해 연계된 뒤 정신과 진료를 받게 되었고, 남편이 첫 평가에 동행했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 앉으세요. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 여기 온 건 배차팀이랑 준법 부서가 컴퓨터 시스템으로 제 노선 변경 사항을 추적해 오고 있다고 생각해서예요. 무전기로도 은근히 이런저런 말들이 오가고요, 특정 운전기사들이 저에 대해 보고하고 있다는 걸 알 수 있어요, 사람들은 계속 그냥 평범한 감독일 뿐이라고 하는데도요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 배차팀이나 다른 운전기사들과 관련해서 이런 일들을 알아차린 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 이제 두 달쯤 됐어요. 그때부터 컴퓨터 추적이랑 무전기에서 오가는 말들이 저한테 꽤 분명하게 느껴지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 주변에 아무도 없을 때, 혹은 다른 사람들은 듣지 못하는데 목소리나 소리를 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 아무도 없을 때 목소리나 소리를 들은 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지난 두 달 동안 기분은 어떠셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] '기분'이 정확히 무슨 뜻인지 잘 모르겠어요. 저는 주로 직장에서 벌어지고 있는 일에 집중해 왔거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 본인 외부의 누군가 또는 무언가가 본인의 머릿속에 생각을 집어넣거나, 몸을 조종하고 있다고 느낀 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 아니요, 누가 제 머릿속에 생각을 집어넣는다거나 제 몸을 조종한다는 느낌은 아니에요. 그보다는 배차팀이랑 준법 부서가 제가 하는 일—노선 변경이나 무전기 발언 같은 걸—추적하고 있고, 다른 운전기사들 몇 명이 저에 대해 보고하고 있다는 걸 알 수 있다는 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 최근에 오락용 약물을 사용하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] '오락용 약물'이 무슨 뜻이신지 잘 모르겠어요. 딱히 그런 걸 알아차린 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 다른 신체적인 질환이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 없는 것 같아요. 무슨 질환이 있다는 얘기를 들은 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 지난 두 달 전까지는, 평소에 다른 사람들을 믿기 어렵다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 보통은 그냥 사람들을 있는 그대로 받아들이는 편이었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+배경 서술: 낸시가 상사의 장기 휴직 기간 동안 임시 배차 팀장을 맡아달라는 요청을 받았을 때, 그 역할은 처음에는 승진으로 이어질 수 있는 구조화된 도전처럼 보였다. 이후 8개월 동안 노선과 준법 관련 감시가 늘어나면서 고정된 믿음이 자리 잡기 시작했고, 직장과 익숙한 커뮤니티 자리에서 그녀의 행동은 점점 상황에 어울리지 않게 되었으며, 성가대, 소프트볼, 손님 초대, 자원봉사 기획에서도 손을 떼게 되었다. 늦여름 무렵에는 노선 보고서가 지연되고, 운전기사들은 그녀의 지시를 따르기 어렵다고 불평했으며, 남편은 집에서 그녀가 의지하던 정돈된 일상이 대부분 무너졌다는 것을 알아챘다. 그녀는 직장에서 직원 지원 프로그램을 통해 연계된 뒤 정신과 진료를 받게 되었고, 남편이 첫 평가에 동행했다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S022 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
+        </is>
+      </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
-  누락: 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
+          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D005_S001_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S001_P001__gemini-3.8-flash_kor.xlsx
@@ -733,6 +733,11 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -767,11 +772,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D005_S001_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S001_P001__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.7708</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9583</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.8125</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
